--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/France National_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/France National_20242025.xlsx
@@ -26235,10 +26235,10 @@
         <v>3</v>
       </c>
       <c r="BB118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD118" t="n">
         <v>0</v>
@@ -26668,13 +26668,13 @@
         <v>8</v>
       </c>
       <c r="BA120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB120" t="n">
         <v>3</v>
       </c>
       <c r="BC120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD120" t="n">
         <v>0</v>
@@ -58379,7 +58379,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>['85', '88']</t>
+          <t>['85', '89']</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
@@ -58478,19 +58478,19 @@
         <v>2.4</v>
       </c>
       <c r="AU266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW266" t="n">
         <v>4</v>
       </c>
-      <c r="AV266" t="n">
+      <c r="AX266" t="n">
         <v>6</v>
       </c>
-      <c r="AW266" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX266" t="n">
-        <v>5</v>
-      </c>
       <c r="AY266" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ266" t="n">
         <v>11</v>
@@ -58597,7 +58597,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>['28', '62', '77']</t>
+          <t>['28', '61', '77']</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
@@ -58696,22 +58696,22 @@
         <v>2.28</v>
       </c>
       <c r="AU267" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV267" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW267" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY267" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AZ267" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BA267" t="n">
         <v>10</v>
@@ -59038,7 +59038,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="Q269" t="n">
@@ -59132,7 +59132,7 @@
         <v>2.55</v>
       </c>
       <c r="AU269" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV269" t="n">
         <v>6</v>
@@ -59144,7 +59144,7 @@
         <v>3</v>
       </c>
       <c r="AY269" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ269" t="n">
         <v>9</v>
@@ -59350,22 +59350,22 @@
         <v>2.62</v>
       </c>
       <c r="AU270" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV270" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX270" t="n">
         <v>3</v>
       </c>
       <c r="AY270" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ270" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA270" t="n">
         <v>4</v>
@@ -59571,19 +59571,19 @@
         <v>4</v>
       </c>
       <c r="AV271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW271" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ271" t="n">
         <v>8</v>
-      </c>
-      <c r="AX271" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY271" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ271" t="n">
-        <v>6</v>
       </c>
       <c r="BA271" t="n">
         <v>8</v>
@@ -59687,7 +59687,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -59792,13 +59792,13 @@
         <v>2</v>
       </c>
       <c r="AW272" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX272" t="n">
         <v>7</v>
       </c>
       <c r="AY272" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ272" t="n">
         <v>9</v>
@@ -60004,22 +60004,22 @@
         <v>2.28</v>
       </c>
       <c r="AU273" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV273" t="n">
         <v>3</v>
       </c>
       <c r="AW273" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX273" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY273" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ273" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA273" t="n">
         <v>9</v>
